--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00878-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00878-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8475B5B-6650-4DD7-9DB1-C82C85FB58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C6CD0F5-734E-489A-95CC-492CAEBA2A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FE5F6A50-09AA-4446-96C3-CA4752C3E79D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D75D87CE-75B6-44A3-BBCF-2383242F695A}"/>
   </bookViews>
   <sheets>
     <sheet name="00878-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1582,20 +1582,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751300F2-4AFC-4F8C-B030-763E4E2282B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BF3EDB-C2A5-4769-B287-33C6F611EC45}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1623,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1653,7 +1653,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1749,7 +1749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1829,7 +1829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="49" t="s">
         <v>65</v>
       </c>
